--- a/artfynd/A 24846-2025 artfynd.xlsx
+++ b/artfynd/A 24846-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136143711</v>
       </c>
       <c r="B3" t="n">
-        <v>93072</v>
+        <v>93075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>136143714</v>
       </c>
       <c r="B6" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>136143716</v>
       </c>
       <c r="B7" t="n">
-        <v>100368</v>
+        <v>100371</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 24846-2025 artfynd.xlsx
+++ b/artfynd/A 24846-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136143711</v>
       </c>
       <c r="B3" t="n">
-        <v>93075</v>
+        <v>93076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>136143714</v>
       </c>
       <c r="B6" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>136143716</v>
       </c>
       <c r="B7" t="n">
-        <v>100371</v>
+        <v>100372</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 24846-2025 artfynd.xlsx
+++ b/artfynd/A 24846-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136143709</v>
       </c>
       <c r="B2" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136143711</v>
       </c>
       <c r="B3" t="n">
-        <v>93076</v>
+        <v>93081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136143710</v>
       </c>
       <c r="B4" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>136143714</v>
       </c>
       <c r="B6" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>136143716</v>
       </c>
       <c r="B7" t="n">
-        <v>100372</v>
+        <v>100377</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
